--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20222.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -79,10 +79,19 @@
     <t>ACEVEDO</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>VALENCIA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>YARELI</t>
+  </si>
+  <si>
+    <t>YARED</t>
   </si>
 </sst>
 </file>
@@ -857,7 +866,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -895,10 +904,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -907,6 +916,29 @@
         <v>9</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920076</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20222.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -76,16 +76,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ARGÜELLO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>ACEVEDO</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>NARANJO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
     <t>VALENCIA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>ATZIN HEFZIBA</t>
+  </si>
+  <si>
+    <t>MARIA TERESA</t>
   </si>
   <si>
     <t>YARELI</t>
@@ -866,7 +881,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -898,16 +913,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920251</v>
+        <v>21330051920253</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -921,16 +936,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920076</v>
+        <v>21330051920260</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -940,6 +955,52 @@
       </c>
       <c r="G3">
         <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920251</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920076</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20222.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20222.xlsx
@@ -530,10 +530,10 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>7</v>
@@ -542,7 +542,7 @@
         <v>25</v>
       </c>
       <c r="G3">
-        <v>75.76000000000001</v>
+        <v>73.53</v>
       </c>
       <c r="H3">
         <v>6.9</v>
@@ -670,10 +670,10 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3">
         <v>32</v>
@@ -804,10 +804,10 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>8</v>
@@ -816,7 +816,7 @@
         <v>25</v>
       </c>
       <c r="G3">
-        <v>75.76000000000001</v>
+        <v>73.53</v>
       </c>
       <c r="H3">
         <v>6.8</v>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20222.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -79,19 +79,25 @@
     <t>ARGÜELLO</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>NARANJO</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>NARANJO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
+    <t>GOMEZ</t>
   </si>
   <si>
     <t>VALENCIA</t>
@@ -100,13 +106,16 @@
     <t>ATZIN HEFZIBA</t>
   </si>
   <si>
-    <t>MARIA TERESA</t>
+    <t>YARED</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
   </si>
   <si>
     <t>YARELI</t>
-  </si>
-  <si>
-    <t>YARED</t>
   </si>
 </sst>
 </file>
@@ -881,7 +890,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -919,10 +928,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -936,16 +945,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920260</v>
+        <v>21330051920076</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -959,47 +968,70 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920251</v>
+        <v>21330051920147</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920076</v>
+        <v>21330051920382</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920251</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20222.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -76,10 +76,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ARGÜELLO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>RAMIREZ</t>
@@ -88,34 +88,28 @@
     <t>SALAZAR</t>
   </si>
   <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>NARANJO</t>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>ATZIN HEFZIBA</t>
-  </si>
-  <si>
-    <t>YARED</t>
+    <t>ALONDRA YURIDIA</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
   </si>
   <si>
     <t>RONALDO</t>
   </si>
   <si>
     <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>YARELI</t>
   </si>
 </sst>
 </file>
@@ -542,16 +536,16 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>7</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>73.53</v>
+        <v>76.47</v>
       </c>
       <c r="H3">
         <v>6.9</v>
@@ -659,16 +653,19 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>95.12</v>
+      </c>
+      <c r="H2">
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -682,16 +679,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>67.65000000000001</v>
+      </c>
+      <c r="H3">
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -705,16 +705,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>64</v>
+      </c>
+      <c r="H4">
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -728,16 +731,19 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>71.43000000000001</v>
+      </c>
+      <c r="H5">
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -793,16 +799,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G2">
-        <v>90.23999999999999</v>
+        <v>95.12</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -816,19 +822,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>73.53</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -845,16 +851,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -880,7 +886,7 @@
         <v>71.43000000000001</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -890,7 +896,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -922,22 +928,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920253</v>
+        <v>21330051920100</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -945,16 +951,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920076</v>
+        <v>21330051920102</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -974,10 +980,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -997,10 +1003,10 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1010,29 +1016,6 @@
       </c>
       <c r="G5">
         <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920251</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20222.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20222.xlsx
@@ -82,34 +82,34 @@
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>SANJUAN</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
     <t>MORENO</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>ALONDRA YURIDIA</t>
   </si>
   <si>
     <t>ANGEL DAVID</t>
   </si>
   <si>
+    <t>ALMA KAREN</t>
+  </si>
+  <si>
     <t>RONALDO</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
   </si>
 </sst>
 </file>
@@ -974,7 +974,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920147</v>
+        <v>21330051920103</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
@@ -989,7 +989,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -997,7 +997,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920382</v>
+        <v>21330051920147</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20222.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -76,37 +76,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SANJUAN</t>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>ALONDRA YURIDIA</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>ALMA KAREN</t>
+    <t>MIROSLAVA</t>
   </si>
   <si>
     <t>RONALDO</t>
@@ -808,7 +790,7 @@
         <v>95.12</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -825,13 +807,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>67.65000000000001</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H3">
         <v>6.7</v>
@@ -851,16 +833,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -886,7 +868,7 @@
         <v>71.43000000000001</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -896,7 +878,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -928,16 +910,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920100</v>
+        <v>21330051920078</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
         <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -951,70 +933,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920102</v>
+        <v>21330051920147</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
         <v>24</v>
       </c>
-      <c r="D3" t="s">
-        <v>28</v>
-      </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920103</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920147</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
         <v>2</v>
       </c>
     </row>
